--- a/data/trans_orig/P21D4_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P21D4_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitándolo, no pudo recibir atención médica mental (psicólogo) en 2023</t>
+          <t>Población que, necesitándolo, no pudo recibir atención médica mental (psicólogo) en 2023 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>237152</t>
+          <t>238412</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>256657</t>
+          <t>257167</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>279690</t>
+          <t>280058</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>290592</t>
+          <t>290810</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>523835</t>
+          <t>520865</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>544317</t>
+          <t>544188</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,19%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6696</t>
+          <t>6852</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24593</t>
+          <t>24589</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7018</t>
+          <t>6998</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17255</t>
+          <t>17210</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16931</t>
+          <t>16296</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36229</t>
+          <t>38143</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>738</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8329</t>
+          <t>10420</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4178</t>
+          <t>4193</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1460</t>
+          <t>1380</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10154</t>
+          <t>10946</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3826</t>
+          <t>4086</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2870</t>
+          <t>2916</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4485</t>
+          <t>4562</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>148587</t>
+          <t>142406</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>629960</t>
+          <t>627491</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>396498</t>
+          <t>397532</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>417041</t>
+          <t>416758</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>388007</t>
+          <t>418728</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1034565</t>
+          <t>1033693</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,53%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27190</t>
+          <t>28854</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>509657</t>
+          <t>515143</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22502</t>
+          <t>22979</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41548</t>
+          <t>41498</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61293</t>
+          <t>61202</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>716349</t>
+          <t>682330</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>61,74%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4679</t>
+          <t>4759</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7592</t>
+          <t>7473</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1724</t>
+          <t>1723</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9639</t>
+          <t>9389</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2960</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1565</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8305</t>
+          <t>7365</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7906</t>
+          <t>8062</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>290378</t>
+          <t>291962</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>315422</t>
+          <t>315821</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>284997</t>
+          <t>285662</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>306351</t>
+          <t>306556</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>587739</t>
+          <t>587619</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>618587</t>
+          <t>617176</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,56%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10841</t>
+          <t>10852</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>34472</t>
+          <t>33483</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16106</t>
+          <t>15794</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33254</t>
+          <t>33005</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>29300</t>
+          <t>30678</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>57736</t>
+          <t>57402</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10287</t>
+          <t>9009</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2523</t>
+          <t>2509</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16726</t>
+          <t>18120</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5325</t>
+          <t>5119</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20391</t>
+          <t>20228</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6584</t>
+          <t>4186</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>167</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4853</t>
+          <t>4276</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>746</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7408</t>
+          <t>7361</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>368581</t>
+          <t>368440</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>390708</t>
+          <t>390055</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>452715</t>
+          <t>454074</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>485124</t>
+          <t>487654</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>830533</t>
+          <t>832341</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>869511</t>
+          <t>869912</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,02%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12661</t>
+          <t>13470</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>32076</t>
+          <t>32567</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>24356</t>
+          <t>23359</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>51266</t>
+          <t>50463</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>43298</t>
+          <t>42094</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>77833</t>
+          <t>75074</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,11%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>779</t>
+          <t>759</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10034</t>
+          <t>10178</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1474</t>
+          <t>1403</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8662</t>
+          <t>8389</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3581</t>
+          <t>3696</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>13917</t>
+          <t>15676</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5920</t>
+          <t>6076</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3269</t>
+          <t>3502</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14560</t>
+          <t>14425</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4396</t>
+          <t>4775</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>16139</t>
+          <t>16310</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>802902</t>
+          <t>828706</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1565734</t>
+          <t>1568296</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1439505</t>
+          <t>1439125</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1483893</t>
+          <t>1482893</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2126661</t>
+          <t>2136189</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3024900</t>
+          <t>3025062</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>80366</t>
+          <t>78781</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>854336</t>
+          <t>825986</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>83613</t>
+          <t>86001</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>123125</t>
+          <t>122883</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>184223</t>
+          <t>184734</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1093766</t>
+          <t>1078507</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,13%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5424</t>
+          <t>5547</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20295</t>
+          <t>21209</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>9243</t>
+          <t>9070</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>25749</t>
+          <t>25261</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>17796</t>
+          <t>17485</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>41642</t>
+          <t>39242</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>796</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>8695</t>
+          <t>9442</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>8255</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>20783</t>
+          <t>21203</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>10170</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>24816</t>
+          <t>26447</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21D4_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P21D4_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>249412</t>
+          <t>270022</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>238412</t>
+          <t>257291</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>257167</t>
+          <t>277973</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>286030</t>
+          <t>309057</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>280058</t>
+          <t>302408</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>290810</t>
+          <t>314443</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>535440</t>
+          <t>579079</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>520865</t>
+          <t>565202</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>544188</t>
+          <t>589500</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,38%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13380</t>
+          <t>14275</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6852</t>
+          <t>7006</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24589</t>
+          <t>25909</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11325</t>
+          <t>12531</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6998</t>
+          <t>7683</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17210</t>
+          <t>18985</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>24705</t>
+          <t>26806</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16296</t>
+          <t>17002</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38143</t>
+          <t>40115</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3115</t>
+          <t>3166</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>742</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10420</t>
+          <t>8543</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1196</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4193</t>
+          <t>4428</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>4311</t>
+          <t>4439</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>1780</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10946</t>
+          <t>10071</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>660</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4086</t>
+          <t>4367</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>648</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2916</t>
+          <t>3479</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4562</t>
+          <t>4462</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>266599</t>
+          <t>288123</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>266599</t>
+          <t>288123</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>266599</t>
+          <t>288123</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>299129</t>
+          <t>323509</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>299129</t>
+          <t>323509</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>299129</t>
+          <t>323509</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>565727</t>
+          <t>611632</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>565727</t>
+          <t>611632</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>565727</t>
+          <t>611632</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>391512</t>
+          <t>445731</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>142406</t>
+          <t>430937</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>627491</t>
+          <t>453927</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>408464</t>
+          <t>461041</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>397532</t>
+          <t>448413</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>416758</t>
+          <t>471345</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>799977</t>
+          <t>906771</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>418728</t>
+          <t>887644</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033693</t>
+          <t>920287</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>94,58%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>265678</t>
+          <t>23215</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28854</t>
+          <t>15333</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>515143</t>
+          <t>38293</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>31071</t>
+          <t>33772</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22979</t>
+          <t>24143</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41498</t>
+          <t>46150</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>296749</t>
+          <t>56987</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61202</t>
+          <t>43903</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>682330</t>
+          <t>74454</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4759</t>
+          <t>4553</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3432</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1376</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7473</t>
+          <t>7773</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>4795</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1723</t>
+          <t>2141</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9389</t>
+          <t>9284</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3805</t>
+          <t>4457</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>1873</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7365</t>
+          <t>9114</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>3805</t>
+          <t>4457</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1223</t>
+          <t>1921</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8062</t>
+          <t>9264</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>658389</t>
+          <t>470208</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>658389</t>
+          <t>470208</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>658389</t>
+          <t>470208</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>446772</t>
+          <t>502802</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>446772</t>
+          <t>502802</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>446772</t>
+          <t>502802</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1105162</t>
+          <t>973010</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1105162</t>
+          <t>973010</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1105162</t>
+          <t>973010</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>306805</t>
+          <t>350196</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>291962</t>
+          <t>334521</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>315821</t>
+          <t>359311</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>298155</t>
+          <t>342632</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>285662</t>
+          <t>330132</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>306556</t>
+          <t>352842</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>604959</t>
+          <t>692827</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>587619</t>
+          <t>672442</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>617176</t>
+          <t>705294</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,46%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18894</t>
+          <t>21209</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10852</t>
+          <t>12829</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>33483</t>
+          <t>35765</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22936</t>
+          <t>25838</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15794</t>
+          <t>17142</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33005</t>
+          <t>36432</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>41830</t>
+          <t>47047</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>30678</t>
+          <t>34823</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>57402</t>
+          <t>63950</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4135</t>
+          <t>4184</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9009</t>
+          <t>10064</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6228</t>
+          <t>7742</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2509</t>
+          <t>3370</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18120</t>
+          <t>16648</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>10363</t>
+          <t>11926</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5119</t>
+          <t>6291</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20228</t>
+          <t>20895</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>995</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2212,12 +2212,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4186</t>
+          <t>5586</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>1841</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>506</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4276</t>
+          <t>5028</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,17 +2272,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2510</t>
+          <t>2836</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>731</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7361</t>
+          <t>7339</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>330838</t>
+          <t>376584</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>330838</t>
+          <t>376584</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>330838</t>
+          <t>376584</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>328824</t>
+          <t>378053</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>328824</t>
+          <t>378053</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>328824</t>
+          <t>378053</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>659661</t>
+          <t>754636</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>659661</t>
+          <t>754636</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>659661</t>
+          <t>754636</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>381754</t>
+          <t>405925</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>368440</t>
+          <t>393540</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>390055</t>
+          <t>415189</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>468289</t>
+          <t>436516</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>454074</t>
+          <t>422432</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>487654</t>
+          <t>447739</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>850042</t>
+          <t>842442</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>832341</t>
+          <t>823398</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>869912</t>
+          <t>859147</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,04%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>21139</t>
+          <t>22042</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13470</t>
+          <t>13877</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>32567</t>
+          <t>33737</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>37839</t>
+          <t>41816</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>23359</t>
+          <t>31657</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>50463</t>
+          <t>55575</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>58978</t>
+          <t>63859</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>42094</t>
+          <t>49744</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>75074</t>
+          <t>80513</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>729</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10178</t>
+          <t>11876</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>4343</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>1615</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8389</t>
+          <t>9426</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,22 +2728,22 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>7379</t>
+          <t>8004</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3696</t>
+          <t>3726</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>15676</t>
+          <t>15891</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6076</t>
+          <t>5864</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>7178</t>
+          <t>7335</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3502</t>
+          <t>3670</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14425</t>
+          <t>14878</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>8862</t>
+          <t>9066</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4775</t>
+          <t>4868</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>16310</t>
+          <t>17044</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>407953</t>
+          <t>433359</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>407953</t>
+          <t>433359</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>407953</t>
+          <t>433359</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>517309</t>
+          <t>490010</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>517309</t>
+          <t>490010</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>517309</t>
+          <t>490010</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>925261</t>
+          <t>923370</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>925261</t>
+          <t>923370</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>925261</t>
+          <t>923370</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1329482</t>
+          <t>1471874</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>828706</t>
+          <t>1445332</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1568296</t>
+          <t>1492768</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1460937</t>
+          <t>1549245</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1439125</t>
+          <t>1527462</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1482893</t>
+          <t>1568694</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>2790419</t>
+          <t>3021119</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2136189</t>
+          <t>2987565</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3025062</t>
+          <t>3047101</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>93,39%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>319090</t>
+          <t>80741</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>78781</t>
+          <t>61816</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>825986</t>
+          <t>106024</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>103172</t>
+          <t>113957</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>86001</t>
+          <t>96882</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>122883</t>
+          <t>133502</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>422262</t>
+          <t>194698</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>184734</t>
+          <t>168733</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1078507</t>
+          <t>223399</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>11825</t>
+          <t>12274</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5547</t>
+          <t>6079</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>21209</t>
+          <t>21208</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>14859</t>
+          <t>16890</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>9070</t>
+          <t>10710</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>25261</t>
+          <t>27816</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>26684</t>
+          <t>29164</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>17485</t>
+          <t>20270</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>39242</t>
+          <t>43107</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>1149</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>9442</t>
+          <t>8584</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,67 +3375,67 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>13066</t>
+          <t>14282</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>7828</t>
+          <t>8822</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>21203</t>
+          <t>21994</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>17667</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>11739</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>26607</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
           <t>0,82%</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>16447</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>10170</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>26447</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="W27" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1592034</t>
+          <t>1694374</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1592034</t>
+          <t>1694374</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1592034</t>
+          <t>1694374</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>3255812</t>
+          <t>3262648</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3255812</t>
+          <t>3262648</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3255812</t>
+          <t>3262648</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
